--- a/backend/data/financials_by_company/0702.HK.xlsx
+++ b/backend/data/financials_by_company/0702.HK.xlsx
@@ -672,58 +672,58 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45291</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-227062250</v>
+        <v>-227336.580506</v>
       </c>
       <c r="C2" t="n">
-        <v>0.25</v>
+        <v>0.00091</v>
       </c>
       <c r="D2" t="n">
-        <v>234064000</v>
+        <v>-225251000</v>
       </c>
       <c r="E2" t="n">
-        <v>-901441000</v>
+        <v>-249861000</v>
       </c>
       <c r="F2" t="n">
-        <v>-908249000</v>
+        <v>-249861000</v>
       </c>
       <c r="G2" t="n">
-        <v>-1086976000</v>
+        <v>-788667000</v>
       </c>
       <c r="H2" t="n">
-        <v>115031000</v>
+        <v>81028000</v>
       </c>
       <c r="I2" t="n">
-        <v>187997000</v>
+        <v>332753000</v>
       </c>
       <c r="J2" t="n">
-        <v>-667377000</v>
+        <v>-475112000</v>
       </c>
       <c r="K2" t="n">
-        <v>-782408000</v>
+        <v>-556140000</v>
       </c>
       <c r="L2" t="n">
-        <v>-268047000</v>
+        <v>-215476000</v>
       </c>
       <c r="M2" t="n">
-        <v>263363000</v>
+        <v>230801000</v>
       </c>
       <c r="N2" t="n">
-        <v>184000</v>
+        <v>27021000</v>
       </c>
       <c r="O2" t="n">
-        <v>-398981250</v>
+        <v>-539033336.580506</v>
       </c>
       <c r="P2" t="n">
-        <v>-1086976000</v>
+        <v>-788667000</v>
       </c>
       <c r="Q2" t="n">
-        <v>238785000</v>
+        <v>706163000</v>
       </c>
       <c r="R2" t="n">
-        <v>-775388000</v>
+        <v>-544454000</v>
       </c>
       <c r="S2" t="n">
         <v>3345439000</v>
@@ -732,94 +732,94 @@
         <v>3345439000</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.3249</v>
+        <v>-0.2357</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.3249</v>
+        <v>-0.2357</v>
       </c>
       <c r="W2" t="n">
-        <v>-1086976000</v>
+        <v>-788667000</v>
       </c>
       <c r="X2" t="n">
-        <v>-1086976000</v>
+        <v>-788667000</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>-1086976000</v>
+        <v>-788667000</v>
       </c>
       <c r="AA2" t="n">
-        <v>2467000</v>
+        <v>-2442000</v>
       </c>
       <c r="AB2" t="n">
-        <v>-1089443000</v>
+        <v>-786225000</v>
       </c>
       <c r="AC2" t="n">
-        <v>-1089443000</v>
+        <v>-786225000</v>
       </c>
       <c r="AD2" t="n">
-        <v>43672000</v>
+        <v>-716000</v>
       </c>
       <c r="AE2" t="n">
-        <v>-1045771000</v>
+        <v>-786941000</v>
       </c>
       <c r="AF2" t="n">
-        <v>1182000</v>
+        <v>-9811000</v>
       </c>
       <c r="AG2" t="n">
-        <v>-896286000</v>
+        <v>-256287000</v>
       </c>
       <c r="AH2" t="n">
-        <v>-2034000</v>
+        <v>136219000</v>
       </c>
       <c r="AI2" t="n">
-        <v>24463000</v>
+        <v>43785000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>867049000</v>
+        <v>76283000</v>
       </c>
       <c r="AK2" t="n">
-        <v>-268047000</v>
+        <v>-215476000</v>
       </c>
       <c r="AL2" t="n">
-        <v>4868000</v>
+        <v>11696000</v>
       </c>
       <c r="AM2" t="n">
-        <v>263363000</v>
+        <v>230801000</v>
       </c>
       <c r="AN2" t="n">
-        <v>184000</v>
+        <v>27021000</v>
       </c>
       <c r="AO2" t="n">
-        <v>131392000</v>
+        <v>-311927000</v>
       </c>
       <c r="AP2" t="n">
-        <v>50788000</v>
+        <v>373410000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>4514000</v>
+        <v>344853000</v>
       </c>
       <c r="AR2" t="n">
-        <v>57682000</v>
+        <v>48169000</v>
       </c>
       <c r="AS2" t="n">
-        <v>15872000</v>
+        <v>15016000</v>
       </c>
       <c r="AT2" t="n">
-        <v>41810000</v>
+        <v>33153000</v>
       </c>
       <c r="AU2" t="n">
-        <v>182180000</v>
+        <v>61483000</v>
       </c>
       <c r="AV2" t="n">
-        <v>187997000</v>
+        <v>332753000</v>
       </c>
       <c r="AW2" t="n">
-        <v>370177000</v>
+        <v>394236000</v>
       </c>
       <c r="AX2" t="n">
-        <v>370177000</v>
+        <v>394236000</v>
       </c>
     </row>
     <row r="3">
@@ -976,58 +976,58 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44561</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-227336.580506</v>
+        <v>-227062250</v>
       </c>
       <c r="C4" t="n">
-        <v>0.00091</v>
+        <v>0.25</v>
       </c>
       <c r="D4" t="n">
-        <v>-225251000</v>
+        <v>234064000</v>
       </c>
       <c r="E4" t="n">
-        <v>-249861000</v>
+        <v>-901441000</v>
       </c>
       <c r="F4" t="n">
-        <v>-249861000</v>
+        <v>-908249000</v>
       </c>
       <c r="G4" t="n">
-        <v>-788667000</v>
+        <v>-1086976000</v>
       </c>
       <c r="H4" t="n">
-        <v>81028000</v>
+        <v>115031000</v>
       </c>
       <c r="I4" t="n">
-        <v>332753000</v>
+        <v>187997000</v>
       </c>
       <c r="J4" t="n">
-        <v>-475112000</v>
+        <v>-667377000</v>
       </c>
       <c r="K4" t="n">
-        <v>-556140000</v>
+        <v>-782408000</v>
       </c>
       <c r="L4" t="n">
-        <v>-215476000</v>
+        <v>-268047000</v>
       </c>
       <c r="M4" t="n">
-        <v>230801000</v>
+        <v>263363000</v>
       </c>
       <c r="N4" t="n">
-        <v>27021000</v>
+        <v>184000</v>
       </c>
       <c r="O4" t="n">
-        <v>-539033336.580506</v>
+        <v>-398981250</v>
       </c>
       <c r="P4" t="n">
-        <v>-788667000</v>
+        <v>-1086976000</v>
       </c>
       <c r="Q4" t="n">
-        <v>706163000</v>
+        <v>238785000</v>
       </c>
       <c r="R4" t="n">
-        <v>-544454000</v>
+        <v>-775388000</v>
       </c>
       <c r="S4" t="n">
         <v>3345439000</v>
@@ -1036,94 +1036,94 @@
         <v>3345439000</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2357</v>
+        <v>-0.3249</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.2357</v>
+        <v>-0.3249</v>
       </c>
       <c r="W4" t="n">
-        <v>-788667000</v>
+        <v>-1086976000</v>
       </c>
       <c r="X4" t="n">
-        <v>-788667000</v>
+        <v>-1086976000</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>-788667000</v>
+        <v>-1086976000</v>
       </c>
       <c r="AA4" t="n">
-        <v>-2442000</v>
+        <v>2467000</v>
       </c>
       <c r="AB4" t="n">
-        <v>-786225000</v>
+        <v>-1089443000</v>
       </c>
       <c r="AC4" t="n">
-        <v>-786225000</v>
+        <v>-1089443000</v>
       </c>
       <c r="AD4" t="n">
-        <v>-716000</v>
+        <v>43672000</v>
       </c>
       <c r="AE4" t="n">
-        <v>-786941000</v>
+        <v>-1045771000</v>
       </c>
       <c r="AF4" t="n">
-        <v>-9811000</v>
+        <v>1182000</v>
       </c>
       <c r="AG4" t="n">
-        <v>-256287000</v>
+        <v>-896286000</v>
       </c>
       <c r="AH4" t="n">
-        <v>136219000</v>
+        <v>-2034000</v>
       </c>
       <c r="AI4" t="n">
-        <v>43785000</v>
+        <v>24463000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>76283000</v>
+        <v>867049000</v>
       </c>
       <c r="AK4" t="n">
-        <v>-215476000</v>
+        <v>-268047000</v>
       </c>
       <c r="AL4" t="n">
-        <v>11696000</v>
+        <v>4868000</v>
       </c>
       <c r="AM4" t="n">
-        <v>230801000</v>
+        <v>263363000</v>
       </c>
       <c r="AN4" t="n">
-        <v>27021000</v>
+        <v>184000</v>
       </c>
       <c r="AO4" t="n">
-        <v>-311927000</v>
+        <v>131392000</v>
       </c>
       <c r="AP4" t="n">
-        <v>373410000</v>
+        <v>50788000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>344853000</v>
+        <v>4514000</v>
       </c>
       <c r="AR4" t="n">
-        <v>48169000</v>
+        <v>57682000</v>
       </c>
       <c r="AS4" t="n">
-        <v>15016000</v>
+        <v>15872000</v>
       </c>
       <c r="AT4" t="n">
-        <v>33153000</v>
+        <v>41810000</v>
       </c>
       <c r="AU4" t="n">
-        <v>61483000</v>
+        <v>182180000</v>
       </c>
       <c r="AV4" t="n">
-        <v>332753000</v>
+        <v>187997000</v>
       </c>
       <c r="AW4" t="n">
-        <v>394236000</v>
+        <v>370177000</v>
       </c>
       <c r="AX4" t="n">
-        <v>394236000</v>
+        <v>370177000</v>
       </c>
     </row>
   </sheetData>
@@ -1479,52 +1479,52 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45291</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>3345439069</v>
+        <v>3345439000</v>
       </c>
       <c r="C2" t="n">
-        <v>3345439069</v>
+        <v>3345439000</v>
       </c>
       <c r="D2" t="n">
-        <v>2080055000</v>
+        <v>2137059000</v>
       </c>
       <c r="E2" t="n">
-        <v>2164518000</v>
+        <v>2157091000</v>
       </c>
       <c r="F2" t="n">
-        <v>-1623619000</v>
+        <v>-372865000</v>
       </c>
       <c r="G2" t="n">
-        <v>1983636000</v>
+        <v>4061536000</v>
       </c>
       <c r="H2" t="n">
-        <v>-2945576000</v>
+        <v>-2276475000</v>
       </c>
       <c r="I2" t="n">
-        <v>-1623619000</v>
+        <v>-372865000</v>
       </c>
       <c r="J2" t="n">
-        <v>3129000</v>
+        <v>6232000</v>
       </c>
       <c r="K2" t="n">
-        <v>-177753000</v>
+        <v>1910677000</v>
       </c>
       <c r="L2" t="n">
-        <v>188216000</v>
+        <v>2411727000</v>
       </c>
       <c r="M2" t="n">
-        <v>-169355000</v>
+        <v>1924207000</v>
       </c>
       <c r="N2" t="n">
-        <v>8398000</v>
+        <v>13530000</v>
       </c>
       <c r="O2" t="n">
-        <v>-177753000</v>
+        <v>1910677000</v>
       </c>
       <c r="P2" t="n">
-        <v>-4450352000</v>
+        <v>-2811597000</v>
       </c>
       <c r="Q2" t="n">
         <v>4567481000</v>
@@ -1536,147 +1536,151 @@
         <v>334544000</v>
       </c>
       <c r="T2" t="n">
-        <v>3901119000</v>
+        <v>3247553000</v>
       </c>
       <c r="U2" t="n">
-        <v>761287000</v>
+        <v>819187000</v>
       </c>
       <c r="V2" t="n">
-        <v>358981000</v>
+        <v>288083000</v>
       </c>
       <c r="W2" t="n">
-        <v>3669000</v>
+        <v>7727000</v>
       </c>
       <c r="X2" t="n">
-        <v>367902000</v>
+        <v>501859000</v>
       </c>
       <c r="Y2" t="n">
-        <v>1933000</v>
+        <v>809000</v>
       </c>
       <c r="Z2" t="n">
-        <v>365969000</v>
+        <v>501050000</v>
       </c>
       <c r="AA2" t="n">
-        <v>30735000</v>
+        <v>21518000</v>
       </c>
       <c r="AB2" t="n">
-        <v>3139832000</v>
+        <v>2428366000</v>
       </c>
       <c r="AC2" t="n">
-        <v>1796616000</v>
+        <v>1655232000</v>
       </c>
       <c r="AD2" t="n">
-        <v>1196000</v>
+        <v>5423000</v>
       </c>
       <c r="AE2" t="n">
-        <v>1795420000</v>
+        <v>1649809000</v>
       </c>
       <c r="AF2" t="n">
-        <v>1316292000</v>
+        <v>756430000</v>
       </c>
       <c r="AG2" t="n">
-        <v>1217190000</v>
+        <v>737140000</v>
       </c>
       <c r="AH2" t="n">
-        <v>97171000</v>
+        <v>9613000</v>
       </c>
       <c r="AI2" t="n">
-        <v>1931000</v>
+        <v>9677000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>3731764000</v>
+        <v>5171760000</v>
       </c>
       <c r="AK2" t="n">
-        <v>3537508000</v>
+        <v>5019869000</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>20698000</v>
       </c>
       <c r="AM2" t="n">
-        <v>93000</v>
+        <v>13554000</v>
       </c>
       <c r="AN2" t="n">
-        <v>93000</v>
+        <v>346000</v>
       </c>
       <c r="AO2" t="n">
-        <v>0</v>
+        <v>13208000</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>22294000</v>
       </c>
       <c r="AQ2" t="n">
         <v>0</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>22294000</v>
       </c>
       <c r="AS2" t="n">
-        <v>1445866000</v>
+        <v>2283542000</v>
       </c>
       <c r="AT2" t="n">
-        <v>1445866000</v>
+        <v>2271096000</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>12446000</v>
       </c>
       <c r="AV2" t="n">
-        <v>2077392000</v>
+        <v>2658964000</v>
       </c>
       <c r="AW2" t="n">
-        <v>-1107544000</v>
+        <v>-272647000</v>
       </c>
       <c r="AX2" t="n">
-        <v>3184936000</v>
+        <v>2931611000</v>
       </c>
       <c r="AY2" t="n">
-        <v>94196000</v>
-      </c>
-      <c r="AZ2" t="inlineStr"/>
+        <v>37080000</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>3740000</v>
+      </c>
       <c r="BA2" t="n">
-        <v>21260000</v>
+        <v>21438000</v>
       </c>
       <c r="BB2" t="n">
-        <v>5669000</v>
-      </c>
-      <c r="BC2" t="inlineStr"/>
+        <v>4131000</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>2865222000</v>
+      </c>
       <c r="BD2" t="n">
-        <v>194256000</v>
+        <v>151891000</v>
       </c>
       <c r="BE2" t="n">
-        <v>1436000</v>
+        <v>912000</v>
       </c>
       <c r="BF2" t="n">
-        <v>15249000</v>
+        <v>1254000</v>
       </c>
       <c r="BG2" t="n">
-        <v>13702000</v>
+        <v>13323000</v>
       </c>
       <c r="BH2" t="n">
-        <v>13702000</v>
+        <v>13323000</v>
       </c>
       <c r="BI2" t="n">
-        <v>26466000</v>
+        <v>42298000</v>
       </c>
       <c r="BJ2" t="n">
-        <v>55959000</v>
+        <v>64194000</v>
       </c>
       <c r="BK2" t="n">
-        <v>-305000</v>
+        <v>-340000</v>
       </c>
       <c r="BL2" t="n">
-        <v>56264000</v>
+        <v>64534000</v>
       </c>
       <c r="BM2" t="n">
-        <v>81444000</v>
+        <v>29910000</v>
       </c>
       <c r="BN2" t="n">
-        <v>110000</v>
+        <v>16110000</v>
       </c>
       <c r="BO2" t="n">
-        <v>81334000</v>
+        <v>13800000</v>
       </c>
       <c r="BP2" t="n">
-        <v>81334000</v>
+        <v>13800000</v>
       </c>
     </row>
     <row r="3">
@@ -1885,52 +1889,52 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44561</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>3345439000</v>
+        <v>3345439069</v>
       </c>
       <c r="C4" t="n">
-        <v>3345439000</v>
+        <v>3345439069</v>
       </c>
       <c r="D4" t="n">
-        <v>2137059000</v>
+        <v>2080055000</v>
       </c>
       <c r="E4" t="n">
-        <v>2157091000</v>
+        <v>2164518000</v>
       </c>
       <c r="F4" t="n">
-        <v>-372865000</v>
+        <v>-1623619000</v>
       </c>
       <c r="G4" t="n">
-        <v>4061536000</v>
+        <v>1983636000</v>
       </c>
       <c r="H4" t="n">
-        <v>-2276475000</v>
+        <v>-2945576000</v>
       </c>
       <c r="I4" t="n">
-        <v>-372865000</v>
+        <v>-1623619000</v>
       </c>
       <c r="J4" t="n">
-        <v>6232000</v>
+        <v>3129000</v>
       </c>
       <c r="K4" t="n">
-        <v>1910677000</v>
+        <v>-177753000</v>
       </c>
       <c r="L4" t="n">
-        <v>2411727000</v>
+        <v>188216000</v>
       </c>
       <c r="M4" t="n">
-        <v>1924207000</v>
+        <v>-169355000</v>
       </c>
       <c r="N4" t="n">
-        <v>13530000</v>
+        <v>8398000</v>
       </c>
       <c r="O4" t="n">
-        <v>1910677000</v>
+        <v>-177753000</v>
       </c>
       <c r="P4" t="n">
-        <v>-2811597000</v>
+        <v>-4450352000</v>
       </c>
       <c r="Q4" t="n">
         <v>4567481000</v>
@@ -1942,151 +1946,147 @@
         <v>334544000</v>
       </c>
       <c r="T4" t="n">
-        <v>3247553000</v>
+        <v>3901119000</v>
       </c>
       <c r="U4" t="n">
-        <v>819187000</v>
+        <v>761287000</v>
       </c>
       <c r="V4" t="n">
-        <v>288083000</v>
+        <v>358981000</v>
       </c>
       <c r="W4" t="n">
-        <v>7727000</v>
+        <v>3669000</v>
       </c>
       <c r="X4" t="n">
-        <v>501859000</v>
+        <v>367902000</v>
       </c>
       <c r="Y4" t="n">
-        <v>809000</v>
+        <v>1933000</v>
       </c>
       <c r="Z4" t="n">
-        <v>501050000</v>
+        <v>365969000</v>
       </c>
       <c r="AA4" t="n">
-        <v>21518000</v>
+        <v>30735000</v>
       </c>
       <c r="AB4" t="n">
-        <v>2428366000</v>
+        <v>3139832000</v>
       </c>
       <c r="AC4" t="n">
-        <v>1655232000</v>
+        <v>1796616000</v>
       </c>
       <c r="AD4" t="n">
-        <v>5423000</v>
+        <v>1196000</v>
       </c>
       <c r="AE4" t="n">
-        <v>1649809000</v>
+        <v>1795420000</v>
       </c>
       <c r="AF4" t="n">
-        <v>756430000</v>
+        <v>1316292000</v>
       </c>
       <c r="AG4" t="n">
-        <v>737140000</v>
+        <v>1217190000</v>
       </c>
       <c r="AH4" t="n">
-        <v>9613000</v>
+        <v>97171000</v>
       </c>
       <c r="AI4" t="n">
-        <v>9677000</v>
+        <v>1931000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>5171760000</v>
+        <v>3731764000</v>
       </c>
       <c r="AK4" t="n">
-        <v>5019869000</v>
+        <v>3537508000</v>
       </c>
       <c r="AL4" t="n">
-        <v>20698000</v>
+        <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>13554000</v>
+        <v>93000</v>
       </c>
       <c r="AN4" t="n">
-        <v>346000</v>
+        <v>93000</v>
       </c>
       <c r="AO4" t="n">
-        <v>13208000</v>
+        <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>22294000</v>
+        <v>0</v>
       </c>
       <c r="AQ4" t="n">
         <v>0</v>
       </c>
       <c r="AR4" t="n">
-        <v>22294000</v>
+        <v>0</v>
       </c>
       <c r="AS4" t="n">
-        <v>2283542000</v>
+        <v>1445866000</v>
       </c>
       <c r="AT4" t="n">
-        <v>2271096000</v>
+        <v>1445866000</v>
       </c>
       <c r="AU4" t="n">
-        <v>12446000</v>
+        <v>0</v>
       </c>
       <c r="AV4" t="n">
-        <v>2658964000</v>
+        <v>2077392000</v>
       </c>
       <c r="AW4" t="n">
-        <v>-272647000</v>
+        <v>-1107544000</v>
       </c>
       <c r="AX4" t="n">
-        <v>2931611000</v>
+        <v>3184936000</v>
       </c>
       <c r="AY4" t="n">
-        <v>37080000</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>3740000</v>
-      </c>
+        <v>94196000</v>
+      </c>
+      <c r="AZ4" t="inlineStr"/>
       <c r="BA4" t="n">
-        <v>21438000</v>
+        <v>21260000</v>
       </c>
       <c r="BB4" t="n">
-        <v>4131000</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>2865222000</v>
-      </c>
+        <v>5669000</v>
+      </c>
+      <c r="BC4" t="inlineStr"/>
       <c r="BD4" t="n">
-        <v>151891000</v>
+        <v>194256000</v>
       </c>
       <c r="BE4" t="n">
-        <v>912000</v>
+        <v>1436000</v>
       </c>
       <c r="BF4" t="n">
-        <v>1254000</v>
+        <v>15249000</v>
       </c>
       <c r="BG4" t="n">
-        <v>13323000</v>
+        <v>13702000</v>
       </c>
       <c r="BH4" t="n">
-        <v>13323000</v>
+        <v>13702000</v>
       </c>
       <c r="BI4" t="n">
-        <v>42298000</v>
+        <v>26466000</v>
       </c>
       <c r="BJ4" t="n">
-        <v>64194000</v>
+        <v>55959000</v>
       </c>
       <c r="BK4" t="n">
-        <v>-340000</v>
+        <v>-305000</v>
       </c>
       <c r="BL4" t="n">
-        <v>64534000</v>
+        <v>56264000</v>
       </c>
       <c r="BM4" t="n">
-        <v>29910000</v>
+        <v>81444000</v>
       </c>
       <c r="BN4" t="n">
-        <v>16110000</v>
+        <v>110000</v>
       </c>
       <c r="BO4" t="n">
-        <v>13800000</v>
+        <v>81334000</v>
       </c>
       <c r="BP4" t="n">
-        <v>13800000</v>
+        <v>81334000</v>
       </c>
     </row>
   </sheetData>
@@ -2317,129 +2317,131 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45291</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>25678000</v>
+        <v>-24704000</v>
       </c>
       <c r="C2" t="n">
-        <v>-84023000</v>
+        <v>-104266000</v>
       </c>
       <c r="D2" t="n">
-        <v>44316000</v>
+        <v>95075000</v>
       </c>
       <c r="E2" t="n">
-        <v>-207822000</v>
+        <v>-202623000</v>
       </c>
       <c r="F2" t="n">
-        <v>81334000</v>
+        <v>13800000</v>
       </c>
       <c r="G2" t="n">
-        <v>78364000</v>
+        <v>60898000</v>
       </c>
       <c r="H2" t="n">
-        <v>-16851000</v>
+        <v>-20845000</v>
       </c>
       <c r="I2" t="n">
-        <v>19821000</v>
+        <v>-26253000</v>
       </c>
       <c r="J2" t="n">
-        <v>-71873000</v>
+        <v>-94388000</v>
       </c>
       <c r="K2" t="n">
-        <v>35000</v>
+        <v>-19263000</v>
       </c>
       <c r="L2" t="n">
-        <v>-31558000</v>
+        <v>-58927000</v>
       </c>
       <c r="M2" t="n">
-        <v>-39707000</v>
+        <v>-9191000</v>
       </c>
       <c r="N2" t="n">
-        <v>-39707000</v>
+        <v>-9191000</v>
       </c>
       <c r="O2" t="n">
-        <v>-84023000</v>
+        <v>-104266000</v>
       </c>
       <c r="P2" t="n">
-        <v>44316000</v>
+        <v>95075000</v>
       </c>
       <c r="Q2" t="n">
-        <v>-141806000</v>
-      </c>
-      <c r="R2" t="inlineStr"/>
+        <v>-109784000</v>
+      </c>
+      <c r="R2" t="n">
+        <v>19280000</v>
+      </c>
       <c r="S2" t="n">
-        <v>184000</v>
+        <v>1791000</v>
       </c>
       <c r="T2" t="n">
-        <v>10106000</v>
+        <v>24438000</v>
       </c>
       <c r="U2" t="n">
-        <v>10216000</v>
+        <v>24438000</v>
       </c>
       <c r="V2" t="n">
-        <v>-110000</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>58895000</v>
+        <v>45766000</v>
       </c>
       <c r="X2" t="n">
-        <v>58895000</v>
+        <v>45766000</v>
       </c>
       <c r="Y2" t="n">
-        <v>-207741000</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>81000</v>
-      </c>
+        <v>-202623000</v>
+      </c>
+      <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="n">
-        <v>-207822000</v>
+        <v>-202623000</v>
       </c>
       <c r="AB2" t="n">
-        <v>233500000</v>
+        <v>177919000</v>
       </c>
       <c r="AC2" t="n">
-        <v>-1603000</v>
+        <v>-1070000</v>
       </c>
       <c r="AD2" t="n">
-        <v>-10457000</v>
+        <v>64750000</v>
       </c>
       <c r="AE2" t="n">
-        <v>4000</v>
+        <v>-104000</v>
       </c>
       <c r="AF2" t="n">
-        <v>-32068000</v>
+        <v>16814000</v>
       </c>
       <c r="AG2" t="n">
-        <v>-185000</v>
+        <v>-2654000</v>
       </c>
       <c r="AH2" t="n">
-        <v>21792000</v>
+        <v>50694000</v>
       </c>
       <c r="AI2" t="n">
-        <v>259603000</v>
+        <v>212486000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>4514000</v>
+        <v>344853000</v>
       </c>
       <c r="AK2" t="n">
-        <v>115031000</v>
+        <v>81028000</v>
       </c>
       <c r="AL2" t="n">
-        <v>38171000</v>
+        <v>24170000</v>
       </c>
       <c r="AM2" t="n">
-        <v>76860000</v>
+        <v>56858000</v>
       </c>
       <c r="AN2" t="n">
-        <v>11792000</v>
+        <v>142755000</v>
       </c>
       <c r="AO2" t="n">
-        <v>-81000</v>
-      </c>
-      <c r="AP2" t="inlineStr"/>
+        <v>76020000</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>0</v>
+      </c>
       <c r="AQ2" t="n">
-        <v>-1045771000</v>
+        <v>-786941000</v>
       </c>
     </row>
     <row r="3">
@@ -2573,131 +2575,129 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44561</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-24704000</v>
+        <v>25678000</v>
       </c>
       <c r="C4" t="n">
-        <v>-104266000</v>
+        <v>-84023000</v>
       </c>
       <c r="D4" t="n">
-        <v>95075000</v>
+        <v>44316000</v>
       </c>
       <c r="E4" t="n">
-        <v>-202623000</v>
+        <v>-207822000</v>
       </c>
       <c r="F4" t="n">
-        <v>13800000</v>
+        <v>81334000</v>
       </c>
       <c r="G4" t="n">
-        <v>60898000</v>
+        <v>78364000</v>
       </c>
       <c r="H4" t="n">
-        <v>-20845000</v>
+        <v>-16851000</v>
       </c>
       <c r="I4" t="n">
-        <v>-26253000</v>
+        <v>19821000</v>
       </c>
       <c r="J4" t="n">
-        <v>-94388000</v>
+        <v>-71873000</v>
       </c>
       <c r="K4" t="n">
-        <v>-19263000</v>
+        <v>35000</v>
       </c>
       <c r="L4" t="n">
-        <v>-58927000</v>
+        <v>-31558000</v>
       </c>
       <c r="M4" t="n">
-        <v>-9191000</v>
+        <v>-39707000</v>
       </c>
       <c r="N4" t="n">
-        <v>-9191000</v>
+        <v>-39707000</v>
       </c>
       <c r="O4" t="n">
-        <v>-104266000</v>
+        <v>-84023000</v>
       </c>
       <c r="P4" t="n">
-        <v>95075000</v>
+        <v>44316000</v>
       </c>
       <c r="Q4" t="n">
-        <v>-109784000</v>
-      </c>
-      <c r="R4" t="n">
-        <v>19280000</v>
-      </c>
+        <v>-141806000</v>
+      </c>
+      <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
-        <v>1791000</v>
+        <v>184000</v>
       </c>
       <c r="T4" t="n">
-        <v>24438000</v>
+        <v>10106000</v>
       </c>
       <c r="U4" t="n">
-        <v>24438000</v>
+        <v>10216000</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>-110000</v>
       </c>
       <c r="W4" t="n">
-        <v>45766000</v>
+        <v>58895000</v>
       </c>
       <c r="X4" t="n">
-        <v>45766000</v>
+        <v>58895000</v>
       </c>
       <c r="Y4" t="n">
-        <v>-202623000</v>
-      </c>
-      <c r="Z4" t="inlineStr"/>
+        <v>-207741000</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>81000</v>
+      </c>
       <c r="AA4" t="n">
-        <v>-202623000</v>
+        <v>-207822000</v>
       </c>
       <c r="AB4" t="n">
-        <v>177919000</v>
+        <v>233500000</v>
       </c>
       <c r="AC4" t="n">
-        <v>-1070000</v>
+        <v>-1603000</v>
       </c>
       <c r="AD4" t="n">
-        <v>64750000</v>
+        <v>-10457000</v>
       </c>
       <c r="AE4" t="n">
-        <v>-104000</v>
+        <v>4000</v>
       </c>
       <c r="AF4" t="n">
-        <v>16814000</v>
+        <v>-32068000</v>
       </c>
       <c r="AG4" t="n">
-        <v>-2654000</v>
+        <v>-185000</v>
       </c>
       <c r="AH4" t="n">
-        <v>50694000</v>
+        <v>21792000</v>
       </c>
       <c r="AI4" t="n">
-        <v>212486000</v>
+        <v>259603000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>344853000</v>
+        <v>4514000</v>
       </c>
       <c r="AK4" t="n">
-        <v>81028000</v>
+        <v>115031000</v>
       </c>
       <c r="AL4" t="n">
-        <v>24170000</v>
+        <v>38171000</v>
       </c>
       <c r="AM4" t="n">
-        <v>56858000</v>
+        <v>76860000</v>
       </c>
       <c r="AN4" t="n">
-        <v>142755000</v>
+        <v>11792000</v>
       </c>
       <c r="AO4" t="n">
-        <v>76020000</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>0</v>
-      </c>
+        <v>-81000</v>
+      </c>
+      <c r="AP4" t="inlineStr"/>
       <c r="AQ4" t="n">
-        <v>-786941000</v>
+        <v>-1045771000</v>
       </c>
     </row>
   </sheetData>
@@ -3207,192 +3207,192 @@
       </c>
       <c r="CU1" t="inlineStr">
         <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="CV1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="CW1" t="inlineStr">
+        <is>
           <t>regularMarketChangePercent</t>
         </is>
       </c>
-      <c r="CV1" t="inlineStr">
+      <c r="CX1" t="inlineStr">
         <is>
           <t>regularMarketPrice</t>
         </is>
       </c>
-      <c r="CW1" t="inlineStr">
+      <c r="CY1" t="inlineStr">
+        <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="CZ1" t="inlineStr">
+        <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="DA1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="DB1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="DC1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>priceToBook</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
         <is>
           <t>cryptoTradeable</t>
         </is>
       </c>
-      <c r="CX1" t="inlineStr">
+      <c r="DQ1" t="inlineStr">
         <is>
           <t>hasPrePostMarketData</t>
         </is>
       </c>
-      <c r="CY1" t="inlineStr">
+      <c r="DR1" t="inlineStr">
         <is>
           <t>firstTradeDateMilliseconds</t>
         </is>
       </c>
-      <c r="CZ1" t="inlineStr">
-        <is>
-          <t>marketState</t>
-        </is>
-      </c>
-      <c r="DA1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="DB1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="DC1" t="inlineStr">
+      <c r="DS1" t="inlineStr">
         <is>
           <t>regularMarketChange</t>
         </is>
       </c>
-      <c r="DD1" t="inlineStr">
+      <c r="DT1" t="inlineStr">
         <is>
           <t>regularMarketDayRange</t>
         </is>
       </c>
-      <c r="DE1" t="inlineStr">
+      <c r="DU1" t="inlineStr">
         <is>
           <t>fullExchangeName</t>
         </is>
       </c>
-      <c r="DF1" t="inlineStr">
+      <c r="DV1" t="inlineStr">
         <is>
           <t>averageDailyVolume3Month</t>
         </is>
       </c>
-      <c r="DG1" t="inlineStr">
+      <c r="DW1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChange</t>
         </is>
       </c>
-      <c r="DH1" t="inlineStr">
+      <c r="DX1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChangePercent</t>
         </is>
       </c>
-      <c r="DI1" t="inlineStr">
+      <c r="DY1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekRange</t>
         </is>
       </c>
-      <c r="DJ1" t="inlineStr">
+      <c r="DZ1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChange</t>
         </is>
       </c>
-      <c r="DK1" t="inlineStr">
+      <c r="EA1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChangePercent</t>
         </is>
       </c>
-      <c r="DL1" t="inlineStr">
+      <c r="EB1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekChangePercent</t>
         </is>
       </c>
-      <c r="DM1" t="inlineStr">
+      <c r="EC1" t="inlineStr">
         <is>
           <t>earningsTimestampStart</t>
         </is>
       </c>
-      <c r="DN1" t="inlineStr">
+      <c r="ED1" t="inlineStr">
         <is>
           <t>earningsTimestampEnd</t>
         </is>
       </c>
-      <c r="DO1" t="inlineStr">
+      <c r="EE1" t="inlineStr">
         <is>
           <t>isEarningsDateEstimate</t>
         </is>
       </c>
-      <c r="DP1" t="inlineStr">
+      <c r="EF1" t="inlineStr">
         <is>
           <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>priceToBook</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
         </is>
       </c>
       <c r="EG1" t="inlineStr">
@@ -3517,7 +3517,7 @@
         <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.386</v>
+        <v>0.418</v>
       </c>
       <c r="AD2" t="n">
         <v>620000</v>
@@ -3644,7 +3644,7 @@
         <v>0</v>
       </c>
       <c r="BR2" t="n">
-        <v>0.27294624</v>
+        <v>0.24487448</v>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
@@ -3748,143 +3748,143 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="CU2" t="n">
+      <c r="CU2" t="inlineStr">
+        <is>
+          <t>SINO OIL &amp; GAS</t>
+        </is>
+      </c>
+      <c r="CV2" t="inlineStr">
+        <is>
+          <t>Sino Oil and Gas Holdings Limited</t>
+        </is>
+      </c>
+      <c r="CW2" t="n">
         <v>-2.857138</v>
       </c>
-      <c r="CV2" t="n">
+      <c r="CX2" t="n">
         <v>0.034</v>
       </c>
-      <c r="CW2" t="b">
-        <v>0</v>
-      </c>
-      <c r="CX2" t="b">
-        <v>0</v>
-      </c>
-      <c r="CY2" t="n">
+      <c r="CY2" t="inlineStr">
+        <is>
+          <t>PREPRE</t>
+        </is>
+      </c>
+      <c r="CZ2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="DA2" t="n">
+        <v>1743387395</v>
+      </c>
+      <c r="DB2" t="inlineStr">
+        <is>
+          <t>HKG</t>
+        </is>
+      </c>
+      <c r="DC2" t="inlineStr">
+        <is>
+          <t>finmb_7689662</t>
+        </is>
+      </c>
+      <c r="DD2" t="inlineStr">
+        <is>
+          <t>Asia/Hong_Kong</t>
+        </is>
+      </c>
+      <c r="DE2" t="inlineStr">
+        <is>
+          <t>HKT</t>
+        </is>
+      </c>
+      <c r="DF2" t="n">
+        <v>28800000</v>
+      </c>
+      <c r="DG2" t="inlineStr">
+        <is>
+          <t>hk_market</t>
+        </is>
+      </c>
+      <c r="DH2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DI2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM2" t="n">
+        <v>-0.35789475</v>
+      </c>
+      <c r="DN2" t="n">
+        <v>15</v>
+      </c>
+      <c r="DO2" t="n">
+        <v>15</v>
+      </c>
+      <c r="DP2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DQ2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR2" t="n">
         <v>1026351000000</v>
       </c>
-      <c r="CZ2" t="inlineStr">
-        <is>
-          <t>PREPRE</t>
-        </is>
-      </c>
-      <c r="DA2" t="inlineStr">
-        <is>
-          <t>SINO OIL &amp; GAS</t>
-        </is>
-      </c>
-      <c r="DB2" t="inlineStr">
-        <is>
-          <t>Sino Oil and Gas Holdings Limited</t>
-        </is>
-      </c>
-      <c r="DC2" t="n">
+      <c r="DS2" t="n">
         <v>-0.0009999983000000001</v>
       </c>
-      <c r="DD2" t="inlineStr">
+      <c r="DT2" t="inlineStr">
         <is>
           <t>0.034 - 0.034</t>
         </is>
       </c>
-      <c r="DE2" t="inlineStr">
+      <c r="DU2" t="inlineStr">
         <is>
           <t>HKSE</t>
         </is>
       </c>
-      <c r="DF2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DG2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DH2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DI2" t="inlineStr">
+      <c r="DV2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DY2" t="inlineStr">
         <is>
           <t>0.034 - 0.034</t>
         </is>
       </c>
-      <c r="DJ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DK2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DM2" t="n">
+      <c r="DZ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="EB2" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC2" t="n">
         <v>1724843699</v>
       </c>
-      <c r="DN2" t="n">
+      <c r="ED2" t="n">
         <v>1724843699</v>
       </c>
-      <c r="DO2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DP2" t="n">
+      <c r="EE2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EF2" t="n">
         <v>-0.31</v>
-      </c>
-      <c r="DQ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DR2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DS2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DT2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DU2" t="n">
-        <v>-0.35789475</v>
-      </c>
-      <c r="DV2" t="n">
-        <v>15</v>
-      </c>
-      <c r="DW2" t="n">
-        <v>15</v>
-      </c>
-      <c r="DX2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="DY2" t="n">
-        <v>1743387395</v>
-      </c>
-      <c r="DZ2" t="inlineStr">
-        <is>
-          <t>HKG</t>
-        </is>
-      </c>
-      <c r="EA2" t="inlineStr">
-        <is>
-          <t>finmb_7689662</t>
-        </is>
-      </c>
-      <c r="EB2" t="inlineStr">
-        <is>
-          <t>Asia/Hong_Kong</t>
-        </is>
-      </c>
-      <c r="EC2" t="inlineStr">
-        <is>
-          <t>HKT</t>
-        </is>
-      </c>
-      <c r="ED2" t="n">
-        <v>28800000</v>
-      </c>
-      <c r="EE2" t="inlineStr">
-        <is>
-          <t>hk_market</t>
-        </is>
-      </c>
-      <c r="EF2" t="b">
-        <v>0</v>
       </c>
       <c r="EG2" t="inlineStr"/>
     </row>
